--- a/artfynd/A 2451-2024 artfynd.xlsx
+++ b/artfynd/A 2451-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130816702</v>
       </c>
       <c r="B2" t="n">
-        <v>78978</v>
+        <v>78979</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>130816570</v>
       </c>
       <c r="B3" t="n">
-        <v>91775</v>
+        <v>91776</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>130816674</v>
       </c>
       <c r="B4" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>130816854</v>
       </c>
       <c r="B5" t="n">
-        <v>93061</v>
+        <v>93062</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>130816807</v>
       </c>
       <c r="B6" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>130816672</v>
       </c>
       <c r="B7" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>130816671</v>
       </c>
       <c r="B8" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 2451-2024 artfynd.xlsx
+++ b/artfynd/A 2451-2024 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>130816570</v>
       </c>
       <c r="B3" t="n">
-        <v>91776</v>
+        <v>91784</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>130816674</v>
       </c>
       <c r="B4" t="n">
-        <v>92074</v>
+        <v>92082</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>130816854</v>
       </c>
       <c r="B5" t="n">
-        <v>93062</v>
+        <v>93071</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>130816672</v>
       </c>
       <c r="B7" t="n">
-        <v>92074</v>
+        <v>92082</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>130816671</v>
       </c>
       <c r="B8" t="n">
-        <v>92074</v>
+        <v>92082</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 2451-2024 artfynd.xlsx
+++ b/artfynd/A 2451-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Sweco naturvärdesinventering och artinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130816671</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Sweco naturvärdesinventering och artinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130816672</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Sweco naturvärdesinventering och artinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130816674</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Sweco naturvärdesinventering och artinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130816675</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Sweco naturvärdesinventering och artinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130816569</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Sweco naturvärdesinventering och artinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130816570</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>Sweco naturvärdesinventering och artinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130816854</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t>Sweco naturvärdesinventering och artinventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130816807</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,8 +1626,24 @@
           <t>Sweco naturvärdesinventering och artinventering</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130816702</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>